--- a/artfynd/A 2165-2021 artfynd.xlsx
+++ b/artfynd/A 2165-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128144165</v>
       </c>
       <c r="B2" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128144094</v>
       </c>
       <c r="B3" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128143640</v>
       </c>
       <c r="B4" t="n">
-        <v>57830</v>
+        <v>57831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>128143959</v>
       </c>
       <c r="B5" t="n">
-        <v>58210</v>
+        <v>58211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>128144068</v>
       </c>
       <c r="B6" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128143643</v>
       </c>
       <c r="B7" t="n">
-        <v>58210</v>
+        <v>58211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>128144163</v>
       </c>
       <c r="B8" t="n">
-        <v>58002</v>
+        <v>58003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>128144232</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57667</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 2165-2021 artfynd.xlsx
+++ b/artfynd/A 2165-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128144165</v>
       </c>
       <c r="B2" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128144094</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128143640</v>
       </c>
       <c r="B4" t="n">
-        <v>57831</v>
+        <v>57843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>128143959</v>
       </c>
       <c r="B5" t="n">
-        <v>58211</v>
+        <v>58223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>128144068</v>
       </c>
       <c r="B6" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128143643</v>
       </c>
       <c r="B7" t="n">
-        <v>58211</v>
+        <v>58223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>128144163</v>
       </c>
       <c r="B8" t="n">
-        <v>58003</v>
+        <v>58015</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>128144232</v>
       </c>
       <c r="B9" t="n">
-        <v>57667</v>
+        <v>57679</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 2165-2021 artfynd.xlsx
+++ b/artfynd/A 2165-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128144165</v>
       </c>
       <c r="B2" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128144094</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128143640</v>
       </c>
       <c r="B4" t="n">
-        <v>57843</v>
+        <v>57847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>128143959</v>
       </c>
       <c r="B5" t="n">
-        <v>58223</v>
+        <v>58227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>128144068</v>
       </c>
       <c r="B6" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128143643</v>
       </c>
       <c r="B7" t="n">
-        <v>58223</v>
+        <v>58227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>128144163</v>
       </c>
       <c r="B8" t="n">
-        <v>58015</v>
+        <v>58019</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>128144232</v>
       </c>
       <c r="B9" t="n">
-        <v>57679</v>
+        <v>57683</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
